--- a/data/trans_dic/P3A$otraSIcobraNOhogar-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P3A$otraSIcobraNOhogar-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que al menos, otra persona que no reside en el hogar y cobra por ello (no de los ingresos del hogar), se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente otra persona que no reside en el hogar y cobra por ello (no de los ingresos del hogar), se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,38; 8,04</t>
+          <t>4,4; 7,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,79; 9,65</t>
+          <t>6,82; 9,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,28; 8,5</t>
+          <t>6,28; 8,42</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,19</t>
+          <t>0,49; 1,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 1,23</t>
+          <t>0,55; 1,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,07</t>
+          <t>0,59; 1,12</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,53</t>
+          <t>0,56; 3,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,96</t>
+          <t>0,13; 0,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,91</t>
+          <t>0,44; 1,81</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,14</t>
+          <t>1,22; 2,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,83; 2,7</t>
+          <t>1,81; 2,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,67; 2,3</t>
+          <t>1,67; 2,29</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que al menos, otra persona que no reside en el hogar y cobra por ello (no de los ingresos del hogar), se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente otra persona que no reside en el hogar y cobra por ello (no de los ingresos del hogar), se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>22540; 41385</t>
+          <t>22635; 41168</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>51306; 72901</t>
+          <t>51514; 72990</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>79790; 107952</t>
+          <t>79797; 106914</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10885; 27169</t>
+          <t>11213; 28476</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12075; 27560</t>
+          <t>12330; 27673</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26323; 48346</t>
+          <t>26844; 50522</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4052; 22854</t>
+          <t>3646; 20408</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>845; 6355</t>
+          <t>839; 6182</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6017; 24948</t>
+          <t>5716; 23619</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>43497; 74005</t>
+          <t>42058; 74768</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>66697; 98527</t>
+          <t>66077; 98746</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>118476; 163113</t>
+          <t>118688; 162320</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A$otraSIcobraNOhogar-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P3A$otraSIcobraNOhogar-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,4; 7,99</t>
+          <t>4,2; 7,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,82; 9,66</t>
+          <t>6,76; 9,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,28; 8,42</t>
+          <t>5,93; 8,11</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,24</t>
+          <t>0,55; 1,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,24</t>
+          <t>0,62; 1,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,12</t>
+          <t>0,68; 1,19</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,16</t>
+          <t>0,63; 3,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,94</t>
+          <t>0,14; 0,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,81</t>
+          <t>0,46; 2,1</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,17</t>
+          <t>1,38; 2,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 2,7</t>
+          <t>1,99; 2,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,67; 2,29</t>
+          <t>1,83; 2,4</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>30718</t>
+          <t>32513</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>61573</t>
+          <t>65227</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>92290</t>
+          <t>97740</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>22635; 41168</t>
+          <t>24291; 43520</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>51514; 72990</t>
+          <t>55551; 77691</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>79797; 106914</t>
+          <t>83105; 113569</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>18121</t>
+          <t>19355</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>18360</t>
+          <t>20435</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>36482</t>
+          <t>39790</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11213; 28476</t>
+          <t>12280; 29000</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12330; 27673</t>
+          <t>13486; 28875</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26844; 50522</t>
+          <t>29783; 52350</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8669</t>
+          <t>9981</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2579</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11248</t>
+          <t>12838</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3646; 20408</t>
+          <t>4503; 26928</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>839; 6182</t>
+          <t>1045; 6752</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5716; 23619</t>
+          <t>6616; 30390</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>57508</t>
+          <t>61849</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>82512</t>
+          <t>88518</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>140020</t>
+          <t>150367</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>42058; 74768</t>
+          <t>48451; 78347</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>66077; 98746</t>
+          <t>74298; 101584</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>118688; 162320</t>
+          <t>132556; 174006</t>
         </is>
       </c>
     </row>
